--- a/mappings/uom_mapping.xlsx
+++ b/mappings/uom_mapping.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LogisticsUnits → uom.uom'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LogisticsUnits → uom.uom'!$A$1:$H$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -496,7 +496,8 @@
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="12.5" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -532,6 +533,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Related Model</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
@@ -567,7 +573,8 @@
           <t>uom.uom</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Always preserve Exact primary key. Needed for resolving Items.Unit → uom.uom during product migration.</t>
         </is>
@@ -604,7 +611,8 @@
           <t>uom.uom</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Direct mapping. Both control visibility/archival of the unit.</t>
         </is>
@@ -641,7 +649,8 @@
           <t>uom.uom</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Short unit code (e.g. "PC", "KG"). Odoo has no separate code field on uom.uom. Preserve for lookup resolution — Items.Unit references this code to resolve the UoM relationship.</t>
         </is>
@@ -678,7 +687,8 @@
           <t>uom.uom</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Human-readable unit name → Odoo UoM display name (e.g. "Piece", "Kilogram", "Hour").</t>
         </is>
@@ -717,6 +727,11 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>Odoo UoMs are global — uom.uom has no company_id field. Division is irrelevant. If multiple divisions define the same unit code, deduplicate before import.</t>
         </is>
       </c>
@@ -752,7 +767,8 @@
           <t>uom.uom</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Indicates the reference unit per division (Main=1). Informs uom_type derivation: Main=1 → uom_type='reference'. Stored for audit trail.</t>
         </is>
@@ -789,7 +805,8 @@
           <t>uom.uom</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Time frame subtype: yy=Year, mm=Month, wk=Week, dd=Day, hh=Hour, mi=Minute, ss=Second. Only meaningful when Type='T'. Odoo models each time unit as a separate uom.uom record within the Working Time category — this field aids matching.</t>
         </is>
@@ -818,7 +835,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>many2one → uom.category</t>
+          <t>many2one</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -827,6 +844,11 @@
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>uom.category</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Map Exact unit type to Odoo UoM category: T→Working Time, W→Weight, V→Volume, L→Length, O→Unit, A→Unit (no standard Area category in Odoo — create one or fold into Unit). Verify target categories exist before import.</t>
         </is>
@@ -863,7 +885,8 @@
           <t>uom.uom</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Reference, bigger, or smaller relative to the category's reference unit. Derive: Main=1 → 'reference'; others → 'bigger' or 'smaller' based on factor. Each uom.category must have exactly one reference unit.</t>
         </is>
@@ -900,7 +923,8 @@
           <t>uom.uom</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Conversion ratio: 1 × (reference unit) = factor × (this unit). For reference units: factor=1.0. For non-reference units, must be manually determined (e.g. dozen: factor=0.08333 in Unit category). Exact does not store conversion ratios.</t>
         </is>
@@ -937,14 +961,15 @@
           <t>uom.uom</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Rounding precision for computed quantities. Default: 0.01. For indivisible units (pieces): 1.0. For weight/volume: 0.001. Must be configured per unit during migration.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/mappings/uom_mapping.xlsx
+++ b/mappings/uom_mapping.xlsx
@@ -58,12 +58,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00CFE2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CFE2F3"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -555,7 +555,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -591,7 +591,7 @@
           <t>Edm.Boolean</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -629,7 +629,7 @@
           <t>Edm.String</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
@@ -667,7 +667,7 @@
           <t>Edm.String</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -747,7 +747,7 @@
           <t>Edm.Byte</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
@@ -785,7 +785,7 @@
           <t>Edm.String</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
